--- a/evaluation/det_gemini_domain.xlsx
+++ b/evaluation/det_gemini_domain.xlsx
@@ -333,7 +333,7 @@
     <col width="36.300000000000004" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.9745055239904677</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.2421875</v>
+        <v>0.62109375</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.10256410256410256</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.014341085271317831</v>
+        <v>0.3563084736701417</v>
       </c>
     </row>
     <row r="3">
@@ -397,7 +397,7 @@
         <v>0.5064707161446439</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.42857142857142855</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="5">
@@ -445,7 +445,7 @@
         <v>0.47709913681079297</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.44444444444444453</v>
+        <v>0.7065972222222223</v>
       </c>
     </row>
     <row r="8">
@@ -477,7 +477,7 @@
         <v>0.9338106764140311</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.8452380952380952</v>
+        <v>0.9226190476190477</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>0.7425955095750908</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.8541666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -541,7 +541,7 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.7611111111111111</v>
+        <v>0.8805555555555555</v>
       </c>
     </row>
     <row r="14">
@@ -557,7 +557,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.6662698412698412</v>
+        <v>0.8331349206349206</v>
       </c>
     </row>
     <row r="15">
@@ -589,7 +589,7 @@
         <v>1.0</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17">
@@ -637,7 +637,7 @@
         <v>1.0</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9153846153846155</v>
       </c>
     </row>
     <row r="20">
@@ -653,7 +653,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.8783068783068783</v>
+        <v>0.8922784391534391</v>
       </c>
     </row>
     <row r="21">
@@ -669,7 +669,7 @@
         <v>0.45</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.34803921568627455</v>
+        <v>0.5724571078431373</v>
       </c>
     </row>
     <row r="22">
@@ -685,7 +685,7 @@
         <v>0.7692307692307693</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8534883720930233</v>
       </c>
     </row>
     <row r="23">
@@ -701,7 +701,7 @@
         <v>0.9</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.66875</v>
+        <v>0.8040719696969697</v>
       </c>
     </row>
     <row r="24">
@@ -733,7 +733,7 @@
         <v>1.0</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.9613095238095238</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/det_gemini_domain.xlsx
+++ b/evaluation/det_gemini_domain.xlsx
@@ -333,7 +333,7 @@
     <col width="36.300000000000004" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.9745055239904677</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.62109375</v>
+        <v>0.2421875</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.10256410256410256</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.3563084736701417</v>
+        <v>0.010014033680834002</v>
       </c>
     </row>
     <row r="3">
@@ -397,7 +397,7 @@
         <v>0.5064707161446439</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.42857142857142855</v>
       </c>
     </row>
     <row r="5">
@@ -445,7 +445,7 @@
         <v>0.47709913681079297</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.7065972222222223</v>
+        <v>0.43055555555555564</v>
       </c>
     </row>
     <row r="8">
@@ -477,7 +477,7 @@
         <v>0.9338106764140311</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.8452380952380952</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>0.7425955095750908</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.8541666666666667</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="12">
@@ -541,7 +541,7 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.8805555555555555</v>
+        <v>0.7611111111111111</v>
       </c>
     </row>
     <row r="14">
@@ -557,7 +557,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.8331349206349206</v>
+        <v>0.6662698412698412</v>
       </c>
     </row>
     <row r="15">
@@ -589,7 +589,7 @@
         <v>1.0</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6222222222222222</v>
       </c>
     </row>
     <row r="17">
@@ -637,7 +637,7 @@
         <v>1.0</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.9153846153846155</v>
+        <v>0.8376068376068376</v>
       </c>
     </row>
     <row r="20">
@@ -653,7 +653,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.8922784391534391</v>
+        <v>0.7959656084656084</v>
       </c>
     </row>
     <row r="21">
@@ -669,7 +669,7 @@
         <v>0.45</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.5724571078431373</v>
+        <v>0.27734375000000006</v>
       </c>
     </row>
     <row r="22">
@@ -685,7 +685,7 @@
         <v>0.7692307692307693</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.8534883720930233</v>
+        <v>0.7255813953488373</v>
       </c>
     </row>
     <row r="23">
@@ -701,7 +701,7 @@
         <v>0.9</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.8040719696969697</v>
+        <v>0.6282196969696969</v>
       </c>
     </row>
     <row r="24">
@@ -733,7 +733,7 @@
         <v>1.0</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
     </row>
   </sheetData>
